--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -1344,7 +1344,7 @@
         <v>136890042</v>
       </c>
       <c r="B8" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>136890044</v>
       </c>
       <c r="B9" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>136890047</v>
       </c>
       <c r="B10" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136890076</v>
       </c>
       <c r="B11" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>136890063</v>
       </c>
       <c r="B18" t="n">
-        <v>98008</v>
+        <v>98014</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>136890065</v>
       </c>
       <c r="B19" t="n">
-        <v>98008</v>
+        <v>98014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>136890054</v>
       </c>
       <c r="B22" t="n">
-        <v>97965</v>
+        <v>97971</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>136890057</v>
       </c>
       <c r="B23" t="n">
-        <v>97965</v>
+        <v>97971</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>136890059</v>
       </c>
       <c r="B24" t="n">
-        <v>97965</v>
+        <v>97971</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>136890061</v>
       </c>
       <c r="B25" t="n">
-        <v>97965</v>
+        <v>97971</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>136890068</v>
       </c>
       <c r="B26" t="n">
-        <v>97965</v>
+        <v>97971</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>136890070</v>
       </c>
       <c r="B27" t="n">
-        <v>97965</v>
+        <v>97971</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>136890099</v>
       </c>
       <c r="B28" t="n">
-        <v>97965</v>
+        <v>97971</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>136890069</v>
       </c>
       <c r="B32" t="n">
-        <v>97626</v>
+        <v>97632</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>136890028</v>
       </c>
       <c r="B34" t="n">
-        <v>96667</v>
+        <v>96673</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>136890053</v>
       </c>
       <c r="B37" t="n">
-        <v>91889</v>
+        <v>91891</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>136890032</v>
       </c>
       <c r="B50" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>136890033</v>
       </c>
       <c r="B51" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>136890035</v>
       </c>
       <c r="B52" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>136890056</v>
       </c>
       <c r="B53" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>136890071</v>
       </c>
       <c r="B54" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>136890080</v>
       </c>
       <c r="B55" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>136890086</v>
       </c>
       <c r="B56" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>136890091</v>
       </c>
       <c r="B57" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>136890096</v>
       </c>
       <c r="B58" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>136890082</v>
       </c>
       <c r="B62" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>136890048</v>
       </c>
       <c r="B133" t="n">
-        <v>111651</v>
+        <v>111657</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>136890046</v>
       </c>
       <c r="B138" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16533,7 +16533,7 @@
         <v>136890058</v>
       </c>
       <c r="B139" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>136890062</v>
       </c>
       <c r="B140" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>136890067</v>
       </c>
       <c r="B141" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -1344,7 +1344,7 @@
         <v>136890042</v>
       </c>
       <c r="B8" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>136890044</v>
       </c>
       <c r="B9" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>136890047</v>
       </c>
       <c r="B10" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136890076</v>
       </c>
       <c r="B11" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>136890063</v>
       </c>
       <c r="B18" t="n">
-        <v>98014</v>
+        <v>98016</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>136890065</v>
       </c>
       <c r="B19" t="n">
-        <v>98014</v>
+        <v>98016</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>136890054</v>
       </c>
       <c r="B22" t="n">
-        <v>97971</v>
+        <v>97973</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>136890057</v>
       </c>
       <c r="B23" t="n">
-        <v>97971</v>
+        <v>97973</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>136890059</v>
       </c>
       <c r="B24" t="n">
-        <v>97971</v>
+        <v>97973</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>136890061</v>
       </c>
       <c r="B25" t="n">
-        <v>97971</v>
+        <v>97973</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>136890068</v>
       </c>
       <c r="B26" t="n">
-        <v>97971</v>
+        <v>97973</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>136890070</v>
       </c>
       <c r="B27" t="n">
-        <v>97971</v>
+        <v>97973</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>136890099</v>
       </c>
       <c r="B28" t="n">
-        <v>97971</v>
+        <v>97973</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>136890069</v>
       </c>
       <c r="B32" t="n">
-        <v>97632</v>
+        <v>97634</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>136890028</v>
       </c>
       <c r="B34" t="n">
-        <v>96673</v>
+        <v>96675</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>136890053</v>
       </c>
       <c r="B37" t="n">
-        <v>91891</v>
+        <v>91893</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>136890032</v>
       </c>
       <c r="B50" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>136890033</v>
       </c>
       <c r="B51" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>136890035</v>
       </c>
       <c r="B52" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>136890056</v>
       </c>
       <c r="B53" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>136890071</v>
       </c>
       <c r="B54" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>136890080</v>
       </c>
       <c r="B55" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>136890086</v>
       </c>
       <c r="B56" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>136890091</v>
       </c>
       <c r="B57" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>136890096</v>
       </c>
       <c r="B58" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>136890082</v>
       </c>
       <c r="B62" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>136890048</v>
       </c>
       <c r="B133" t="n">
-        <v>111657</v>
+        <v>111659</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>136890046</v>
       </c>
       <c r="B138" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16533,7 +16533,7 @@
         <v>136890058</v>
       </c>
       <c r="B139" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>136890062</v>
       </c>
       <c r="B140" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>136890067</v>
       </c>
       <c r="B141" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -10402,7 +10402,7 @@
         <v>129774299</v>
       </c>
       <c r="B88" t="n">
-        <v>4775</v>
+        <v>4777</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10519,7 +10519,7 @@
         <v>129774305</v>
       </c>
       <c r="B89" t="n">
-        <v>4775</v>
+        <v>4777</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>129774312</v>
       </c>
       <c r="B90" t="n">
-        <v>4775</v>
+        <v>4777</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>129774318</v>
       </c>
       <c r="B91" t="n">
-        <v>4775</v>
+        <v>4777</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>129914767</v>
       </c>
       <c r="B92" t="n">
-        <v>4775</v>
+        <v>4777</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>133641588</v>
       </c>
       <c r="B93" t="n">
-        <v>4776</v>
+        <v>4777</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11117,7 +11117,7 @@
         <v>133641595</v>
       </c>
       <c r="B94" t="n">
-        <v>4776</v>
+        <v>4777</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>133641596</v>
       </c>
       <c r="B95" t="n">
-        <v>4776</v>
+        <v>4777</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -1344,7 +1344,7 @@
         <v>136890042</v>
       </c>
       <c r="B8" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>136890044</v>
       </c>
       <c r="B9" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>136890047</v>
       </c>
       <c r="B10" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136890076</v>
       </c>
       <c r="B11" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>136890063</v>
       </c>
       <c r="B18" t="n">
-        <v>98016</v>
+        <v>98017</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>136890065</v>
       </c>
       <c r="B19" t="n">
-        <v>98016</v>
+        <v>98017</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>136890054</v>
       </c>
       <c r="B22" t="n">
-        <v>97973</v>
+        <v>97974</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>136890057</v>
       </c>
       <c r="B23" t="n">
-        <v>97973</v>
+        <v>97974</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>136890059</v>
       </c>
       <c r="B24" t="n">
-        <v>97973</v>
+        <v>97974</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>136890061</v>
       </c>
       <c r="B25" t="n">
-        <v>97973</v>
+        <v>97974</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>136890068</v>
       </c>
       <c r="B26" t="n">
-        <v>97973</v>
+        <v>97974</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>136890070</v>
       </c>
       <c r="B27" t="n">
-        <v>97973</v>
+        <v>97974</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>136890099</v>
       </c>
       <c r="B28" t="n">
-        <v>97973</v>
+        <v>97974</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>136890069</v>
       </c>
       <c r="B32" t="n">
-        <v>97634</v>
+        <v>97635</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>136890028</v>
       </c>
       <c r="B34" t="n">
-        <v>96675</v>
+        <v>96676</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>136890053</v>
       </c>
       <c r="B37" t="n">
-        <v>91893</v>
+        <v>91894</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>136890032</v>
       </c>
       <c r="B50" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>136890033</v>
       </c>
       <c r="B51" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>136890035</v>
       </c>
       <c r="B52" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>136890056</v>
       </c>
       <c r="B53" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>136890071</v>
       </c>
       <c r="B54" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>136890080</v>
       </c>
       <c r="B55" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>136890086</v>
       </c>
       <c r="B56" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>136890091</v>
       </c>
       <c r="B57" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>136890096</v>
       </c>
       <c r="B58" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>136890082</v>
       </c>
       <c r="B62" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>136890048</v>
       </c>
       <c r="B133" t="n">
-        <v>111659</v>
+        <v>111660</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>136890046</v>
       </c>
       <c r="B138" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16533,7 +16533,7 @@
         <v>136890058</v>
       </c>
       <c r="B139" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>136890062</v>
       </c>
       <c r="B140" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>136890067</v>
       </c>
       <c r="B141" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -1344,7 +1344,7 @@
         <v>136890042</v>
       </c>
       <c r="B8" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>136890044</v>
       </c>
       <c r="B9" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>136890047</v>
       </c>
       <c r="B10" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136890076</v>
       </c>
       <c r="B11" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>136890063</v>
       </c>
       <c r="B18" t="n">
-        <v>98017</v>
+        <v>98023</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>136890065</v>
       </c>
       <c r="B19" t="n">
-        <v>98017</v>
+        <v>98023</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>136890054</v>
       </c>
       <c r="B22" t="n">
-        <v>97974</v>
+        <v>97980</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>136890057</v>
       </c>
       <c r="B23" t="n">
-        <v>97974</v>
+        <v>97980</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>136890059</v>
       </c>
       <c r="B24" t="n">
-        <v>97974</v>
+        <v>97980</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>136890061</v>
       </c>
       <c r="B25" t="n">
-        <v>97974</v>
+        <v>97980</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>136890068</v>
       </c>
       <c r="B26" t="n">
-        <v>97974</v>
+        <v>97980</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>136890070</v>
       </c>
       <c r="B27" t="n">
-        <v>97974</v>
+        <v>97980</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>136890099</v>
       </c>
       <c r="B28" t="n">
-        <v>97974</v>
+        <v>97980</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>136890069</v>
       </c>
       <c r="B32" t="n">
-        <v>97635</v>
+        <v>97641</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>136890028</v>
       </c>
       <c r="B34" t="n">
-        <v>96676</v>
+        <v>96682</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>136890053</v>
       </c>
       <c r="B37" t="n">
-        <v>91894</v>
+        <v>91900</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>136890032</v>
       </c>
       <c r="B50" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>136890033</v>
       </c>
       <c r="B51" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>136890035</v>
       </c>
       <c r="B52" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>136890056</v>
       </c>
       <c r="B53" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>136890071</v>
       </c>
       <c r="B54" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>136890080</v>
       </c>
       <c r="B55" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>136890086</v>
       </c>
       <c r="B56" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>136890091</v>
       </c>
       <c r="B57" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>136890096</v>
       </c>
       <c r="B58" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>136890048</v>
       </c>
       <c r="B133" t="n">
-        <v>111660</v>
+        <v>111666</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>136890046</v>
       </c>
       <c r="B138" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16533,7 +16533,7 @@
         <v>136890058</v>
       </c>
       <c r="B139" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>136890062</v>
       </c>
       <c r="B140" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>136890067</v>
       </c>
       <c r="B141" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -1344,7 +1344,7 @@
         <v>136890042</v>
       </c>
       <c r="B8" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>136890044</v>
       </c>
       <c r="B9" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>136890047</v>
       </c>
       <c r="B10" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136890076</v>
       </c>
       <c r="B11" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>136890063</v>
       </c>
       <c r="B18" t="n">
-        <v>98023</v>
+        <v>98027</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>136890065</v>
       </c>
       <c r="B19" t="n">
-        <v>98023</v>
+        <v>98027</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>136890054</v>
       </c>
       <c r="B22" t="n">
-        <v>97980</v>
+        <v>97984</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>136890057</v>
       </c>
       <c r="B23" t="n">
-        <v>97980</v>
+        <v>97984</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>136890059</v>
       </c>
       <c r="B24" t="n">
-        <v>97980</v>
+        <v>97984</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>136890061</v>
       </c>
       <c r="B25" t="n">
-        <v>97980</v>
+        <v>97984</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>136890068</v>
       </c>
       <c r="B26" t="n">
-        <v>97980</v>
+        <v>97984</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>136890070</v>
       </c>
       <c r="B27" t="n">
-        <v>97980</v>
+        <v>97984</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>136890099</v>
       </c>
       <c r="B28" t="n">
-        <v>97980</v>
+        <v>97984</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>136890069</v>
       </c>
       <c r="B32" t="n">
-        <v>97641</v>
+        <v>97645</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>136890028</v>
       </c>
       <c r="B34" t="n">
-        <v>96682</v>
+        <v>96686</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>136890053</v>
       </c>
       <c r="B37" t="n">
-        <v>91900</v>
+        <v>91904</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>136890032</v>
       </c>
       <c r="B50" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>136890033</v>
       </c>
       <c r="B51" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>136890035</v>
       </c>
       <c r="B52" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>136890056</v>
       </c>
       <c r="B53" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>136890071</v>
       </c>
       <c r="B54" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>136890080</v>
       </c>
       <c r="B55" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>136890086</v>
       </c>
       <c r="B56" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>136890091</v>
       </c>
       <c r="B57" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>136890096</v>
       </c>
       <c r="B58" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>136890082</v>
       </c>
       <c r="B62" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>136890048</v>
       </c>
       <c r="B133" t="n">
-        <v>111666</v>
+        <v>111670</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>136890046</v>
       </c>
       <c r="B138" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16533,7 +16533,7 @@
         <v>136890058</v>
       </c>
       <c r="B139" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>136890062</v>
       </c>
       <c r="B140" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>136890067</v>
       </c>
       <c r="B141" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -1344,7 +1344,7 @@
         <v>136890042</v>
       </c>
       <c r="B8" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>136890044</v>
       </c>
       <c r="B9" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>136890047</v>
       </c>
       <c r="B10" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136890076</v>
       </c>
       <c r="B11" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>136890063</v>
       </c>
       <c r="B18" t="n">
-        <v>98027</v>
+        <v>98029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>136890065</v>
       </c>
       <c r="B19" t="n">
-        <v>98027</v>
+        <v>98029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>136890054</v>
       </c>
       <c r="B22" t="n">
-        <v>97984</v>
+        <v>97986</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>136890057</v>
       </c>
       <c r="B23" t="n">
-        <v>97984</v>
+        <v>97986</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>136890059</v>
       </c>
       <c r="B24" t="n">
-        <v>97984</v>
+        <v>97986</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>136890061</v>
       </c>
       <c r="B25" t="n">
-        <v>97984</v>
+        <v>97986</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>136890068</v>
       </c>
       <c r="B26" t="n">
-        <v>97984</v>
+        <v>97986</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>136890070</v>
       </c>
       <c r="B27" t="n">
-        <v>97984</v>
+        <v>97986</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>136890099</v>
       </c>
       <c r="B28" t="n">
-        <v>97984</v>
+        <v>97986</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>136890069</v>
       </c>
       <c r="B32" t="n">
-        <v>97645</v>
+        <v>97647</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>136890028</v>
       </c>
       <c r="B34" t="n">
-        <v>96686</v>
+        <v>96688</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>136890048</v>
       </c>
       <c r="B133" t="n">
-        <v>111670</v>
+        <v>111672</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>136890046</v>
       </c>
       <c r="B138" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16533,7 +16533,7 @@
         <v>136890058</v>
       </c>
       <c r="B139" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>136890062</v>
       </c>
       <c r="B140" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>136890067</v>
       </c>
       <c r="B141" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -1344,7 +1344,7 @@
         <v>136890042</v>
       </c>
       <c r="B8" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>136890044</v>
       </c>
       <c r="B9" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>136890047</v>
       </c>
       <c r="B10" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136890076</v>
       </c>
       <c r="B11" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>136890063</v>
       </c>
       <c r="B18" t="n">
-        <v>98029</v>
+        <v>98031</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>136890065</v>
       </c>
       <c r="B19" t="n">
-        <v>98029</v>
+        <v>98031</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>136890054</v>
       </c>
       <c r="B22" t="n">
-        <v>97986</v>
+        <v>97988</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>136890057</v>
       </c>
       <c r="B23" t="n">
-        <v>97986</v>
+        <v>97988</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>136890059</v>
       </c>
       <c r="B24" t="n">
-        <v>97986</v>
+        <v>97988</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>136890061</v>
       </c>
       <c r="B25" t="n">
-        <v>97986</v>
+        <v>97988</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>136890068</v>
       </c>
       <c r="B26" t="n">
-        <v>97986</v>
+        <v>97988</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>136890070</v>
       </c>
       <c r="B27" t="n">
-        <v>97986</v>
+        <v>97988</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>136890099</v>
       </c>
       <c r="B28" t="n">
-        <v>97986</v>
+        <v>97988</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>136890069</v>
       </c>
       <c r="B32" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>136890028</v>
       </c>
       <c r="B34" t="n">
-        <v>96688</v>
+        <v>96690</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>136890053</v>
       </c>
       <c r="B37" t="n">
-        <v>91904</v>
+        <v>91906</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>136890032</v>
       </c>
       <c r="B50" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>136890033</v>
       </c>
       <c r="B51" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>136890035</v>
       </c>
       <c r="B52" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>136890056</v>
       </c>
       <c r="B53" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>136890071</v>
       </c>
       <c r="B54" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>136890080</v>
       </c>
       <c r="B55" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>136890086</v>
       </c>
       <c r="B56" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>136890091</v>
       </c>
       <c r="B57" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>136890096</v>
       </c>
       <c r="B58" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>136890082</v>
       </c>
       <c r="B62" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>136890048</v>
       </c>
       <c r="B133" t="n">
-        <v>111672</v>
+        <v>111674</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>136890046</v>
       </c>
       <c r="B138" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16533,7 +16533,7 @@
         <v>136890058</v>
       </c>
       <c r="B139" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>136890062</v>
       </c>
       <c r="B140" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>136890067</v>
       </c>
       <c r="B141" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -1344,7 +1344,7 @@
         <v>136890042</v>
       </c>
       <c r="B8" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>136890044</v>
       </c>
       <c r="B9" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>136890047</v>
       </c>
       <c r="B10" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136890076</v>
       </c>
       <c r="B11" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>136890063</v>
       </c>
       <c r="B18" t="n">
-        <v>98031</v>
+        <v>98044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>136890065</v>
       </c>
       <c r="B19" t="n">
-        <v>98031</v>
+        <v>98044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>136890054</v>
       </c>
       <c r="B22" t="n">
-        <v>97988</v>
+        <v>98001</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>136890057</v>
       </c>
       <c r="B23" t="n">
-        <v>97988</v>
+        <v>98001</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>136890059</v>
       </c>
       <c r="B24" t="n">
-        <v>97988</v>
+        <v>98001</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>136890061</v>
       </c>
       <c r="B25" t="n">
-        <v>97988</v>
+        <v>98001</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>136890068</v>
       </c>
       <c r="B26" t="n">
-        <v>97988</v>
+        <v>98001</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>136890070</v>
       </c>
       <c r="B27" t="n">
-        <v>97988</v>
+        <v>98001</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>136890099</v>
       </c>
       <c r="B28" t="n">
-        <v>97988</v>
+        <v>98001</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>136890069</v>
       </c>
       <c r="B32" t="n">
-        <v>97649</v>
+        <v>97662</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>136890028</v>
       </c>
       <c r="B34" t="n">
-        <v>96690</v>
+        <v>96703</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>136890053</v>
       </c>
       <c r="B37" t="n">
-        <v>91906</v>
+        <v>91919</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>136890032</v>
       </c>
       <c r="B50" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>136890033</v>
       </c>
       <c r="B51" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>136890035</v>
       </c>
       <c r="B52" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>136890056</v>
       </c>
       <c r="B53" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>136890071</v>
       </c>
       <c r="B54" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>136890080</v>
       </c>
       <c r="B55" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>136890086</v>
       </c>
       <c r="B56" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>136890091</v>
       </c>
       <c r="B57" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>136890096</v>
       </c>
       <c r="B58" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>136890082</v>
       </c>
       <c r="B62" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>136890060</v>
       </c>
       <c r="B76" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>136890064</v>
       </c>
       <c r="B77" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>136890072</v>
       </c>
       <c r="B78" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>136890097</v>
       </c>
       <c r="B79" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>136890048</v>
       </c>
       <c r="B133" t="n">
-        <v>111674</v>
+        <v>111687</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>136890046</v>
       </c>
       <c r="B138" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16533,7 +16533,7 @@
         <v>136890058</v>
       </c>
       <c r="B139" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>136890062</v>
       </c>
       <c r="B140" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>136890067</v>
       </c>
       <c r="B141" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -1344,7 +1344,7 @@
         <v>136890042</v>
       </c>
       <c r="B8" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>136890044</v>
       </c>
       <c r="B9" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>136890047</v>
       </c>
       <c r="B10" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136890076</v>
       </c>
       <c r="B11" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>136890063</v>
       </c>
       <c r="B18" t="n">
-        <v>98044</v>
+        <v>98046</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>136890065</v>
       </c>
       <c r="B19" t="n">
-        <v>98044</v>
+        <v>98046</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>136890054</v>
       </c>
       <c r="B22" t="n">
-        <v>98001</v>
+        <v>98003</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>136890057</v>
       </c>
       <c r="B23" t="n">
-        <v>98001</v>
+        <v>98003</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>136890059</v>
       </c>
       <c r="B24" t="n">
-        <v>98001</v>
+        <v>98003</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>136890061</v>
       </c>
       <c r="B25" t="n">
-        <v>98001</v>
+        <v>98003</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>136890068</v>
       </c>
       <c r="B26" t="n">
-        <v>98001</v>
+        <v>98003</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>136890070</v>
       </c>
       <c r="B27" t="n">
-        <v>98001</v>
+        <v>98003</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>136890099</v>
       </c>
       <c r="B28" t="n">
-        <v>98001</v>
+        <v>98003</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>136890069</v>
       </c>
       <c r="B32" t="n">
-        <v>97662</v>
+        <v>97664</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>136890028</v>
       </c>
       <c r="B34" t="n">
-        <v>96703</v>
+        <v>96705</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>136890053</v>
       </c>
       <c r="B37" t="n">
-        <v>91919</v>
+        <v>91921</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>136890032</v>
       </c>
       <c r="B50" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>136890033</v>
       </c>
       <c r="B51" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>136890035</v>
       </c>
       <c r="B52" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>136890056</v>
       </c>
       <c r="B53" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>136890071</v>
       </c>
       <c r="B54" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>136890080</v>
       </c>
       <c r="B55" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>136890086</v>
       </c>
       <c r="B56" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>136890091</v>
       </c>
       <c r="B57" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>136890096</v>
       </c>
       <c r="B58" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>136890082</v>
       </c>
       <c r="B62" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>136890060</v>
       </c>
       <c r="B76" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>136890064</v>
       </c>
       <c r="B77" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>136890072</v>
       </c>
       <c r="B78" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>136890097</v>
       </c>
       <c r="B79" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>136890048</v>
       </c>
       <c r="B133" t="n">
-        <v>111687</v>
+        <v>111689</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>136890046</v>
       </c>
       <c r="B138" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16533,7 +16533,7 @@
         <v>136890058</v>
       </c>
       <c r="B139" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>136890062</v>
       </c>
       <c r="B140" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>136890067</v>
       </c>
       <c r="B141" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -10545,11 +10545,7 @@
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
@@ -10667,11 +10663,7 @@
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
@@ -10789,11 +10781,7 @@
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
@@ -10914,11 +10902,7 @@
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -11025,11 +11009,7 @@
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -11146,11 +11126,7 @@
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -11267,11 +11243,7 @@
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -11385,11 +11357,7 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
@@ -11507,11 +11475,7 @@
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
@@ -11629,11 +11593,7 @@
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
@@ -11751,11 +11711,7 @@
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
@@ -11873,11 +11829,7 @@
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
@@ -11995,11 +11947,7 @@
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
@@ -12117,11 +12065,7 @@
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
@@ -12239,11 +12183,7 @@
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
@@ -12361,11 +12301,7 @@
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
@@ -12483,11 +12419,7 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
@@ -12605,11 +12537,7 @@
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
@@ -12727,11 +12655,7 @@
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
@@ -12849,11 +12773,7 @@
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
@@ -12971,11 +12891,7 @@
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
@@ -13210,11 +13126,7 @@
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
@@ -13332,11 +13244,7 @@
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
@@ -13454,11 +13362,7 @@
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
@@ -13576,11 +13480,7 @@
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
@@ -13698,11 +13598,7 @@
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
@@ -13820,11 +13716,7 @@
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
@@ -13942,11 +13834,7 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
@@ -14670,11 +14558,7 @@
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
@@ -14792,11 +14676,7 @@
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
@@ -14914,11 +14794,7 @@
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
@@ -15036,11 +14912,7 @@
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
@@ -15158,11 +15030,7 @@
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
@@ -15397,11 +15265,7 @@
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
@@ -15519,11 +15383,7 @@
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
@@ -15641,11 +15501,7 @@
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>
@@ -15763,11 +15619,7 @@
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Ebberud, Dls</t>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -1344,7 +1344,7 @@
         <v>136890042</v>
       </c>
       <c r="B8" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>136890044</v>
       </c>
       <c r="B9" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>136890047</v>
       </c>
       <c r="B10" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136890076</v>
       </c>
       <c r="B11" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>136890063</v>
       </c>
       <c r="B18" t="n">
-        <v>98046</v>
+        <v>98049</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>136890065</v>
       </c>
       <c r="B19" t="n">
-        <v>98046</v>
+        <v>98049</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>136890054</v>
       </c>
       <c r="B22" t="n">
-        <v>98003</v>
+        <v>98006</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>136890057</v>
       </c>
       <c r="B23" t="n">
-        <v>98003</v>
+        <v>98006</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>136890059</v>
       </c>
       <c r="B24" t="n">
-        <v>98003</v>
+        <v>98006</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>136890061</v>
       </c>
       <c r="B25" t="n">
-        <v>98003</v>
+        <v>98006</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>136890068</v>
       </c>
       <c r="B26" t="n">
-        <v>98003</v>
+        <v>98006</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>136890070</v>
       </c>
       <c r="B27" t="n">
-        <v>98003</v>
+        <v>98006</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>136890099</v>
       </c>
       <c r="B28" t="n">
-        <v>98003</v>
+        <v>98006</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>136890069</v>
       </c>
       <c r="B32" t="n">
-        <v>97664</v>
+        <v>97667</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>136890028</v>
       </c>
       <c r="B34" t="n">
-        <v>96705</v>
+        <v>96708</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>136890053</v>
       </c>
       <c r="B37" t="n">
-        <v>91921</v>
+        <v>91924</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>136890032</v>
       </c>
       <c r="B50" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>136890033</v>
       </c>
       <c r="B51" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>136890035</v>
       </c>
       <c r="B52" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>136890056</v>
       </c>
       <c r="B53" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>136890071</v>
       </c>
       <c r="B54" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>136890080</v>
       </c>
       <c r="B55" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>136890086</v>
       </c>
       <c r="B56" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>136890091</v>
       </c>
       <c r="B57" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>136890096</v>
       </c>
       <c r="B58" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -15711,7 +15711,7 @@
         <v>136890048</v>
       </c>
       <c r="B133" t="n">
-        <v>111689</v>
+        <v>111695</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16283,7 +16283,7 @@
         <v>136890046</v>
       </c>
       <c r="B138" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
         <v>136890058</v>
       </c>
       <c r="B139" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>136890062</v>
       </c>
       <c r="B140" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>136890067</v>
       </c>
       <c r="B141" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -1344,7 +1344,7 @@
         <v>136890042</v>
       </c>
       <c r="B8" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>136890044</v>
       </c>
       <c r="B9" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>136890047</v>
       </c>
       <c r="B10" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136890076</v>
       </c>
       <c r="B11" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>136890063</v>
       </c>
       <c r="B18" t="n">
-        <v>98049</v>
+        <v>98059</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>136890065</v>
       </c>
       <c r="B19" t="n">
-        <v>98049</v>
+        <v>98059</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>136890054</v>
       </c>
       <c r="B22" t="n">
-        <v>98006</v>
+        <v>98016</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>136890057</v>
       </c>
       <c r="B23" t="n">
-        <v>98006</v>
+        <v>98016</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>136890059</v>
       </c>
       <c r="B24" t="n">
-        <v>98006</v>
+        <v>98016</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>136890061</v>
       </c>
       <c r="B25" t="n">
-        <v>98006</v>
+        <v>98016</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>136890068</v>
       </c>
       <c r="B26" t="n">
-        <v>98006</v>
+        <v>98016</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>136890070</v>
       </c>
       <c r="B27" t="n">
-        <v>98006</v>
+        <v>98016</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>136890099</v>
       </c>
       <c r="B28" t="n">
-        <v>98006</v>
+        <v>98016</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>136890069</v>
       </c>
       <c r="B32" t="n">
-        <v>97667</v>
+        <v>97677</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>136890028</v>
       </c>
       <c r="B34" t="n">
-        <v>96708</v>
+        <v>96718</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>136890053</v>
       </c>
       <c r="B37" t="n">
-        <v>91924</v>
+        <v>91934</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>136890032</v>
       </c>
       <c r="B50" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>136890033</v>
       </c>
       <c r="B51" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>136890035</v>
       </c>
       <c r="B52" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>136890056</v>
       </c>
       <c r="B53" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>136890071</v>
       </c>
       <c r="B54" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>136890080</v>
       </c>
       <c r="B55" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>136890086</v>
       </c>
       <c r="B56" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>136890091</v>
       </c>
       <c r="B57" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>136890096</v>
       </c>
       <c r="B58" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>136890082</v>
       </c>
       <c r="B62" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>136890060</v>
       </c>
       <c r="B76" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>136890064</v>
       </c>
       <c r="B77" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>136890072</v>
       </c>
       <c r="B78" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>136890097</v>
       </c>
       <c r="B79" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         <v>129774299</v>
       </c>
       <c r="B88" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10519,7 +10519,7 @@
         <v>129774305</v>
       </c>
       <c r="B89" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
         <v>129774312</v>
       </c>
       <c r="B90" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>129774318</v>
       </c>
       <c r="B91" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>129914767</v>
       </c>
       <c r="B92" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>133641588</v>
       </c>
       <c r="B93" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>133641595</v>
       </c>
       <c r="B94" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11214,7 +11214,7 @@
         <v>133641596</v>
       </c>
       <c r="B95" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>136890030</v>
       </c>
       <c r="B96" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         <v>136890034</v>
       </c>
       <c r="B97" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>136890036</v>
       </c>
       <c r="B98" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>136890037</v>
       </c>
       <c r="B99" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>136890039</v>
       </c>
       <c r="B100" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         <v>136890055</v>
       </c>
       <c r="B101" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v>136890066</v>
       </c>
       <c r="B102" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         <v>136890074</v>
       </c>
       <c r="B103" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12275,7 +12275,7 @@
         <v>136890075</v>
       </c>
       <c r="B104" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>136890077</v>
       </c>
       <c r="B105" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>136890079</v>
       </c>
       <c r="B106" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12629,7 +12629,7 @@
         <v>136890084</v>
       </c>
       <c r="B107" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>136890085</v>
       </c>
       <c r="B108" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12865,7 +12865,7 @@
         <v>136890087</v>
       </c>
       <c r="B109" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>136890090</v>
       </c>
       <c r="B110" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>136890092</v>
       </c>
       <c r="B111" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         <v>136890095</v>
       </c>
       <c r="B112" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>136890031</v>
       </c>
       <c r="B113" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>136890041</v>
       </c>
       <c r="B114" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         <v>136890051</v>
       </c>
       <c r="B115" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13690,7 +13690,7 @@
         <v>136890088</v>
       </c>
       <c r="B116" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>136890094</v>
       </c>
       <c r="B117" t="n">
-        <v>5181</v>
+        <v>5187</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         <v>136890093</v>
       </c>
       <c r="B118" t="n">
-        <v>4783</v>
+        <v>4789</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14532,7 +14532,7 @@
         <v>136890027</v>
       </c>
       <c r="B123" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
         <v>136890040</v>
       </c>
       <c r="B124" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14768,7 +14768,7 @@
         <v>136890043</v>
       </c>
       <c r="B125" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14886,7 +14886,7 @@
         <v>136890050</v>
       </c>
       <c r="B126" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>136890052</v>
       </c>
       <c r="B127" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>136890073</v>
       </c>
       <c r="B128" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>136890078</v>
       </c>
       <c r="B129" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15357,7 +15357,7 @@
         <v>136890081</v>
       </c>
       <c r="B130" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15475,7 +15475,7 @@
         <v>136890083</v>
       </c>
       <c r="B131" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15593,7 +15593,7 @@
         <v>136890089</v>
       </c>
       <c r="B132" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15711,7 +15711,7 @@
         <v>136890048</v>
       </c>
       <c r="B133" t="n">
-        <v>111695</v>
+        <v>111717</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16283,7 +16283,7 @@
         <v>136890046</v>
       </c>
       <c r="B138" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
         <v>136890058</v>
       </c>
       <c r="B139" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>136890062</v>
       </c>
       <c r="B140" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>136890067</v>
       </c>
       <c r="B141" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -1344,7 +1344,7 @@
         <v>136890042</v>
       </c>
       <c r="B8" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>136890044</v>
       </c>
       <c r="B9" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>136890047</v>
       </c>
       <c r="B10" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136890076</v>
       </c>
       <c r="B11" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>136890063</v>
       </c>
       <c r="B18" t="n">
-        <v>98059</v>
+        <v>98060</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>136890065</v>
       </c>
       <c r="B19" t="n">
-        <v>98059</v>
+        <v>98060</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>136890054</v>
       </c>
       <c r="B22" t="n">
-        <v>98016</v>
+        <v>98017</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>136890057</v>
       </c>
       <c r="B23" t="n">
-        <v>98016</v>
+        <v>98017</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>136890059</v>
       </c>
       <c r="B24" t="n">
-        <v>98016</v>
+        <v>98017</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>136890061</v>
       </c>
       <c r="B25" t="n">
-        <v>98016</v>
+        <v>98017</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>136890068</v>
       </c>
       <c r="B26" t="n">
-        <v>98016</v>
+        <v>98017</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>136890070</v>
       </c>
       <c r="B27" t="n">
-        <v>98016</v>
+        <v>98017</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>136890099</v>
       </c>
       <c r="B28" t="n">
-        <v>98016</v>
+        <v>98017</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>136890069</v>
       </c>
       <c r="B32" t="n">
-        <v>97677</v>
+        <v>97678</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>136890028</v>
       </c>
       <c r="B34" t="n">
-        <v>96718</v>
+        <v>96719</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>136890053</v>
       </c>
       <c r="B37" t="n">
-        <v>91934</v>
+        <v>91935</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>136890032</v>
       </c>
       <c r="B50" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>136890033</v>
       </c>
       <c r="B51" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>136890035</v>
       </c>
       <c r="B52" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>136890056</v>
       </c>
       <c r="B53" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>136890071</v>
       </c>
       <c r="B54" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>136890080</v>
       </c>
       <c r="B55" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>136890086</v>
       </c>
       <c r="B56" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>136890091</v>
       </c>
       <c r="B57" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>136890096</v>
       </c>
       <c r="B58" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -15711,7 +15711,7 @@
         <v>136890048</v>
       </c>
       <c r="B133" t="n">
-        <v>111717</v>
+        <v>111718</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16283,7 +16283,7 @@
         <v>136890046</v>
       </c>
       <c r="B138" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
         <v>136890058</v>
       </c>
       <c r="B139" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>136890062</v>
       </c>
       <c r="B140" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>136890067</v>
       </c>
       <c r="B141" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -1344,7 +1344,7 @@
         <v>136890042</v>
       </c>
       <c r="B8" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>136890044</v>
       </c>
       <c r="B9" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>136890047</v>
       </c>
       <c r="B10" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136890076</v>
       </c>
       <c r="B11" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>136890063</v>
       </c>
       <c r="B18" t="n">
-        <v>98060</v>
+        <v>98065</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>136890065</v>
       </c>
       <c r="B19" t="n">
-        <v>98060</v>
+        <v>98065</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>136890054</v>
       </c>
       <c r="B22" t="n">
-        <v>98017</v>
+        <v>98022</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>136890057</v>
       </c>
       <c r="B23" t="n">
-        <v>98017</v>
+        <v>98022</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>136890059</v>
       </c>
       <c r="B24" t="n">
-        <v>98017</v>
+        <v>98022</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>136890061</v>
       </c>
       <c r="B25" t="n">
-        <v>98017</v>
+        <v>98022</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>136890068</v>
       </c>
       <c r="B26" t="n">
-        <v>98017</v>
+        <v>98022</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>136890070</v>
       </c>
       <c r="B27" t="n">
-        <v>98017</v>
+        <v>98022</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>136890099</v>
       </c>
       <c r="B28" t="n">
-        <v>98017</v>
+        <v>98022</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>136890069</v>
       </c>
       <c r="B32" t="n">
-        <v>97678</v>
+        <v>97683</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>136890028</v>
       </c>
       <c r="B34" t="n">
-        <v>96719</v>
+        <v>96724</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>136890053</v>
       </c>
       <c r="B37" t="n">
-        <v>91935</v>
+        <v>91938</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>136890032</v>
       </c>
       <c r="B50" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>136890033</v>
       </c>
       <c r="B51" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>136890035</v>
       </c>
       <c r="B52" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>136890056</v>
       </c>
       <c r="B53" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>136890071</v>
       </c>
       <c r="B54" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>136890080</v>
       </c>
       <c r="B55" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>136890086</v>
       </c>
       <c r="B56" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>136890091</v>
       </c>
       <c r="B57" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>136890096</v>
       </c>
       <c r="B58" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>136890082</v>
       </c>
       <c r="B62" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>136890060</v>
       </c>
       <c r="B76" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>136890064</v>
       </c>
       <c r="B77" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>136890072</v>
       </c>
       <c r="B78" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>136890097</v>
       </c>
       <c r="B79" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -15711,7 +15711,7 @@
         <v>136890048</v>
       </c>
       <c r="B133" t="n">
-        <v>111718</v>
+        <v>111723</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16283,7 +16283,7 @@
         <v>136890046</v>
       </c>
       <c r="B138" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
         <v>136890058</v>
       </c>
       <c r="B139" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>136890062</v>
       </c>
       <c r="B140" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>136890067</v>
       </c>
       <c r="B141" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -1344,7 +1344,7 @@
         <v>136890042</v>
       </c>
       <c r="B8" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>136890044</v>
       </c>
       <c r="B9" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>136890047</v>
       </c>
       <c r="B10" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136890076</v>
       </c>
       <c r="B11" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>136890063</v>
       </c>
       <c r="B18" t="n">
-        <v>98065</v>
+        <v>98067</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>136890065</v>
       </c>
       <c r="B19" t="n">
-        <v>98065</v>
+        <v>98067</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>136890054</v>
       </c>
       <c r="B22" t="n">
-        <v>98022</v>
+        <v>98024</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>136890057</v>
       </c>
       <c r="B23" t="n">
-        <v>98022</v>
+        <v>98024</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>136890059</v>
       </c>
       <c r="B24" t="n">
-        <v>98022</v>
+        <v>98024</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>136890061</v>
       </c>
       <c r="B25" t="n">
-        <v>98022</v>
+        <v>98024</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>136890068</v>
       </c>
       <c r="B26" t="n">
-        <v>98022</v>
+        <v>98024</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>136890070</v>
       </c>
       <c r="B27" t="n">
-        <v>98022</v>
+        <v>98024</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>136890099</v>
       </c>
       <c r="B28" t="n">
-        <v>98022</v>
+        <v>98024</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>136890069</v>
       </c>
       <c r="B32" t="n">
-        <v>97683</v>
+        <v>97685</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>136890028</v>
       </c>
       <c r="B34" t="n">
-        <v>96724</v>
+        <v>96726</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>136890053</v>
       </c>
       <c r="B37" t="n">
-        <v>91938</v>
+        <v>91940</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>136890032</v>
       </c>
       <c r="B50" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>136890033</v>
       </c>
       <c r="B51" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>136890035</v>
       </c>
       <c r="B52" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>136890056</v>
       </c>
       <c r="B53" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>136890071</v>
       </c>
       <c r="B54" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>136890080</v>
       </c>
       <c r="B55" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>136890086</v>
       </c>
       <c r="B56" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>136890091</v>
       </c>
       <c r="B57" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>136890096</v>
       </c>
       <c r="B58" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -15711,7 +15711,7 @@
         <v>136890048</v>
       </c>
       <c r="B133" t="n">
-        <v>111723</v>
+        <v>111726</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16283,7 +16283,7 @@
         <v>136890046</v>
       </c>
       <c r="B138" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
         <v>136890058</v>
       </c>
       <c r="B139" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>136890062</v>
       </c>
       <c r="B140" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>136890067</v>
       </c>
       <c r="B141" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -1344,7 +1344,7 @@
         <v>136890042</v>
       </c>
       <c r="B8" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>136890044</v>
       </c>
       <c r="B9" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>136890047</v>
       </c>
       <c r="B10" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136890076</v>
       </c>
       <c r="B11" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>136890063</v>
       </c>
       <c r="B18" t="n">
-        <v>98067</v>
+        <v>98073</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>136890065</v>
       </c>
       <c r="B19" t="n">
-        <v>98067</v>
+        <v>98073</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>136890054</v>
       </c>
       <c r="B22" t="n">
-        <v>98024</v>
+        <v>98030</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>136890057</v>
       </c>
       <c r="B23" t="n">
-        <v>98024</v>
+        <v>98030</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>136890059</v>
       </c>
       <c r="B24" t="n">
-        <v>98024</v>
+        <v>98030</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>136890061</v>
       </c>
       <c r="B25" t="n">
-        <v>98024</v>
+        <v>98030</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>136890068</v>
       </c>
       <c r="B26" t="n">
-        <v>98024</v>
+        <v>98030</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>136890070</v>
       </c>
       <c r="B27" t="n">
-        <v>98024</v>
+        <v>98030</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>136890099</v>
       </c>
       <c r="B28" t="n">
-        <v>98024</v>
+        <v>98030</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>136890069</v>
       </c>
       <c r="B32" t="n">
-        <v>97685</v>
+        <v>97691</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>136890028</v>
       </c>
       <c r="B34" t="n">
-        <v>96726</v>
+        <v>96732</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>136890053</v>
       </c>
       <c r="B37" t="n">
-        <v>91940</v>
+        <v>91945</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>136890032</v>
       </c>
       <c r="B50" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>136890033</v>
       </c>
       <c r="B51" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>136890035</v>
       </c>
       <c r="B52" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>136890056</v>
       </c>
       <c r="B53" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>136890071</v>
       </c>
       <c r="B54" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>136890080</v>
       </c>
       <c r="B55" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>136890086</v>
       </c>
       <c r="B56" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>136890091</v>
       </c>
       <c r="B57" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>136890096</v>
       </c>
       <c r="B58" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>136890082</v>
       </c>
       <c r="B62" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>136890060</v>
       </c>
       <c r="B76" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>136890064</v>
       </c>
       <c r="B77" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>136890072</v>
       </c>
       <c r="B78" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>136890097</v>
       </c>
       <c r="B79" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -15711,7 +15711,7 @@
         <v>136890048</v>
       </c>
       <c r="B133" t="n">
-        <v>111726</v>
+        <v>111732</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16283,7 +16283,7 @@
         <v>136890046</v>
       </c>
       <c r="B138" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
         <v>136890058</v>
       </c>
       <c r="B139" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>136890062</v>
       </c>
       <c r="B140" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>136890067</v>
       </c>
       <c r="B141" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -15711,7 +15711,7 @@
         <v>136890048</v>
       </c>
       <c r="B133" t="n">
-        <v>111732</v>
+        <v>111733</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -1344,7 +1344,7 @@
         <v>136890042</v>
       </c>
       <c r="B8" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>136890044</v>
       </c>
       <c r="B9" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>136890047</v>
       </c>
       <c r="B10" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136890076</v>
       </c>
       <c r="B11" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>136890063</v>
       </c>
       <c r="B18" t="n">
-        <v>98073</v>
+        <v>98085</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>136890065</v>
       </c>
       <c r="B19" t="n">
-        <v>98073</v>
+        <v>98085</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>136890054</v>
       </c>
       <c r="B22" t="n">
-        <v>98030</v>
+        <v>98042</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>136890057</v>
       </c>
       <c r="B23" t="n">
-        <v>98030</v>
+        <v>98042</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>136890059</v>
       </c>
       <c r="B24" t="n">
-        <v>98030</v>
+        <v>98042</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>136890061</v>
       </c>
       <c r="B25" t="n">
-        <v>98030</v>
+        <v>98042</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>136890068</v>
       </c>
       <c r="B26" t="n">
-        <v>98030</v>
+        <v>98042</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>136890070</v>
       </c>
       <c r="B27" t="n">
-        <v>98030</v>
+        <v>98042</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>136890099</v>
       </c>
       <c r="B28" t="n">
-        <v>98030</v>
+        <v>98042</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>136890069</v>
       </c>
       <c r="B32" t="n">
-        <v>97691</v>
+        <v>97703</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>136890028</v>
       </c>
       <c r="B34" t="n">
-        <v>96732</v>
+        <v>96744</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>136890053</v>
       </c>
       <c r="B37" t="n">
-        <v>91945</v>
+        <v>91957</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>136890032</v>
       </c>
       <c r="B50" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>136890033</v>
       </c>
       <c r="B51" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>136890035</v>
       </c>
       <c r="B52" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>136890056</v>
       </c>
       <c r="B53" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>136890071</v>
       </c>
       <c r="B54" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>136890080</v>
       </c>
       <c r="B55" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>136890086</v>
       </c>
       <c r="B56" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>136890091</v>
       </c>
       <c r="B57" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>136890096</v>
       </c>
       <c r="B58" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>136890082</v>
       </c>
       <c r="B62" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>136890060</v>
       </c>
       <c r="B76" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>136890064</v>
       </c>
       <c r="B77" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>136890072</v>
       </c>
       <c r="B78" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>136890097</v>
       </c>
       <c r="B79" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -15711,7 +15711,7 @@
         <v>136890048</v>
       </c>
       <c r="B133" t="n">
-        <v>111733</v>
+        <v>111745</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16283,7 +16283,7 @@
         <v>136890046</v>
       </c>
       <c r="B138" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
         <v>136890058</v>
       </c>
       <c r="B139" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>136890062</v>
       </c>
       <c r="B140" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>136890067</v>
       </c>
       <c r="B141" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -1344,7 +1344,7 @@
         <v>136890042</v>
       </c>
       <c r="B8" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>136890044</v>
       </c>
       <c r="B9" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>136890047</v>
       </c>
       <c r="B10" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136890076</v>
       </c>
       <c r="B11" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>136890063</v>
       </c>
       <c r="B18" t="n">
-        <v>98085</v>
+        <v>98086</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>136890065</v>
       </c>
       <c r="B19" t="n">
-        <v>98085</v>
+        <v>98086</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>136890054</v>
       </c>
       <c r="B22" t="n">
-        <v>98042</v>
+        <v>98043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>136890057</v>
       </c>
       <c r="B23" t="n">
-        <v>98042</v>
+        <v>98043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>136890059</v>
       </c>
       <c r="B24" t="n">
-        <v>98042</v>
+        <v>98043</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>136890061</v>
       </c>
       <c r="B25" t="n">
-        <v>98042</v>
+        <v>98043</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>136890068</v>
       </c>
       <c r="B26" t="n">
-        <v>98042</v>
+        <v>98043</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>136890070</v>
       </c>
       <c r="B27" t="n">
-        <v>98042</v>
+        <v>98043</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>136890099</v>
       </c>
       <c r="B28" t="n">
-        <v>98042</v>
+        <v>98043</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>136890069</v>
       </c>
       <c r="B32" t="n">
-        <v>97703</v>
+        <v>97704</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>136890028</v>
       </c>
       <c r="B34" t="n">
-        <v>96744</v>
+        <v>96745</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>136890053</v>
       </c>
       <c r="B37" t="n">
-        <v>91957</v>
+        <v>91958</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>136890032</v>
       </c>
       <c r="B50" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>136890033</v>
       </c>
       <c r="B51" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>136890035</v>
       </c>
       <c r="B52" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>136890056</v>
       </c>
       <c r="B53" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>136890071</v>
       </c>
       <c r="B54" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>136890080</v>
       </c>
       <c r="B55" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>136890086</v>
       </c>
       <c r="B56" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>136890091</v>
       </c>
       <c r="B57" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>136890096</v>
       </c>
       <c r="B58" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>136890082</v>
       </c>
       <c r="B62" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -15711,7 +15711,7 @@
         <v>136890048</v>
       </c>
       <c r="B133" t="n">
-        <v>111745</v>
+        <v>111746</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16283,7 +16283,7 @@
         <v>136890046</v>
       </c>
       <c r="B138" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
         <v>136890058</v>
       </c>
       <c r="B139" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>136890062</v>
       </c>
       <c r="B140" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>136890067</v>
       </c>
       <c r="B141" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>

--- a/artfynd/A 54343-2025 artfynd.xlsx
+++ b/artfynd/A 54343-2025 artfynd.xlsx
@@ -1344,7 +1344,7 @@
         <v>136890042</v>
       </c>
       <c r="B8" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>136890044</v>
       </c>
       <c r="B9" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>136890047</v>
       </c>
       <c r="B10" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136890076</v>
       </c>
       <c r="B11" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>136890063</v>
       </c>
       <c r="B18" t="n">
-        <v>98086</v>
+        <v>98089</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>136890065</v>
       </c>
       <c r="B19" t="n">
-        <v>98086</v>
+        <v>98089</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>136890054</v>
       </c>
       <c r="B22" t="n">
-        <v>98043</v>
+        <v>98046</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>136890057</v>
       </c>
       <c r="B23" t="n">
-        <v>98043</v>
+        <v>98046</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>136890059</v>
       </c>
       <c r="B24" t="n">
-        <v>98043</v>
+        <v>98046</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>136890061</v>
       </c>
       <c r="B25" t="n">
-        <v>98043</v>
+        <v>98046</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>136890068</v>
       </c>
       <c r="B26" t="n">
-        <v>98043</v>
+        <v>98046</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>136890070</v>
       </c>
       <c r="B27" t="n">
-        <v>98043</v>
+        <v>98046</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>136890099</v>
       </c>
       <c r="B28" t="n">
-        <v>98043</v>
+        <v>98046</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>136890069</v>
       </c>
       <c r="B32" t="n">
-        <v>97704</v>
+        <v>97707</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>136890028</v>
       </c>
       <c r="B34" t="n">
-        <v>96745</v>
+        <v>96748</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>136890053</v>
       </c>
       <c r="B37" t="n">
-        <v>91958</v>
+        <v>91961</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>136890032</v>
       </c>
       <c r="B50" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>136890033</v>
       </c>
       <c r="B51" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>136890035</v>
       </c>
       <c r="B52" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>136890056</v>
       </c>
       <c r="B53" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>136890071</v>
       </c>
       <c r="B54" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>136890080</v>
       </c>
       <c r="B55" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>136890086</v>
       </c>
       <c r="B56" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>136890091</v>
       </c>
       <c r="B57" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>136890096</v>
       </c>
       <c r="B58" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>136890082</v>
       </c>
       <c r="B62" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -15711,7 +15711,7 @@
         <v>136890048</v>
       </c>
       <c r="B133" t="n">
-        <v>111746</v>
+        <v>111749</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16283,7 +16283,7 @@
         <v>136890046</v>
       </c>
       <c r="B138" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
         <v>136890058</v>
       </c>
       <c r="B139" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>136890062</v>
       </c>
       <c r="B140" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>136890067</v>
       </c>
       <c r="B141" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
